--- a/etf_holdings/2026-10-29_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,38 +504,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3.59%1300</t>
+          <t>+0.47%6405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3.59%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1300</v>
+        <v>6405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.57%1,299,000</t>
+          <t>7.69%260,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.57%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1299000</v>
+        <v>260000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.77%1100</t>
+          <t>-3.85%1250</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.54%1,530,000</t>
+          <t>7.50%1,299,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.54%</t>
+          <t>7.50%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1530000</v>
+        <v>1299000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+8.79%6375</t>
+          <t>-5.45%1040</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+8.79%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6375</v>
+        <v>1040</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.43%260,000</t>
+          <t>7.35%1,530,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.43%</t>
+          <t>7.35%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>260000</v>
+        <v>1530000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+6.78%5115</t>
+          <t>-5.38%4840</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+6.78%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5115</v>
+        <v>4840</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.40%323,000</t>
+          <t>7.22%323,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>7.22%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+7.99%17295</t>
+          <t>-1.82%16980</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+7.99%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>17295</v>
+        <v>16980</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.07%91,300</t>
+          <t>7.16%91,300</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.07%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.72%1185</t>
+          <t>-5.91%1115</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.72%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1185</v>
+        <v>1115</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.98%1,127,000</t>
+          <t>5.81%1,127,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.98%</t>
+          <t>5.81%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+6.94%4235</t>
+          <t>-4.49%4045</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+6.94%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4235</v>
+        <v>4045</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.58%294,000</t>
+          <t>5.50%294,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.32%1810</t>
+          <t>-5.8%1705</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1810</v>
+        <v>1705</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.39%665,000</t>
+          <t>5.24%665,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+3.13%1815</t>
+          <t>-3.31%1755</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1815</v>
+        <v>1755</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.95%609,000</t>
+          <t>4.94%609,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5.79%5025</t>
+          <t>-0.3%5010</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5025</v>
+        <v>5010</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.77%212,000</t>
+          <t>4.91%212,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.77%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.56%843</t>
+          <t>-0.24%841</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+3.56%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.89%1,030,000</t>
+          <t>4.00%1,030,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+6.81%5565</t>
+          <t>-1.42%2425</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5565</v>
+        <v>2425</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.99%120,000</t>
+          <t>3.04%271,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>120000</v>
+        <v>271000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+9.33%2460</t>
+          <t>-6.74%5190</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+9.33%</t>
+          <t>-6.74%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2460</v>
+        <v>5190</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.99%271,000</t>
+          <t>2.88%120,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>271000</v>
+        <v>120000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.96%8170</t>
+          <t>-6.49%7640</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-6.49%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8170</v>
+        <v>7640</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.67%73,000</t>
+          <t>2.58%73,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:17</t>
+          <t>2026-10-29 23:21:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.47%10150</t>
+          <t>-2.66%9880</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.47%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10150</v>
+        <v>9880</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.27%50,000</t>
+          <t>2.28%50,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.04%2425</t>
+          <t>-0.41%2415</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2425</v>
+        <v>2415</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.94%179,000</t>
+          <t>2.00%179,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+7.42%1375</t>
+          <t>+1.09%1390</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+7.42%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1375</v>
+        <v>1390</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.89%306,000</t>
+          <t>1.97%306,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.72%3215</t>
+          <t>-3.42%3105</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.72%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3215</v>
+        <v>3105</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+8.19%1585</t>
+          <t>-2.52%1545</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1585</v>
+        <v>1545</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.42%200,000</t>
+          <t>1.43%200,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.67%1345</t>
+          <t>-3.33%1885</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1345</v>
+        <v>1885</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.89%148,000</t>
+          <t>0.86%99,139</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>148000</v>
+        <v>99139</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0%1950</t>
+          <t>-6.32%1260</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1950</v>
+        <v>1260</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.87%99,139</t>
+          <t>0.86%148,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>99139</v>
+        <v>148000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.65%1550</t>
+          <t>-4.52%1480</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>-4.52%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1550</v>
+        <v>1480</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.65%94,000</t>
+          <t>0.64%94,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6415矽力*-KY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.35%4935</t>
+          <t>-0.19%524</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4935</v>
+        <v>524</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.51%23,000</t>
+          <t>0.61%250,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>23000</v>
+        <v>250000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+9.99%1035</t>
+          <t>-5.67%4655</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+9.99%</t>
+          <t>-5.67%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1035</v>
+        <v>4655</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.23%50,000</t>
+          <t>0.49%23,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>50000</v>
+        <v>23000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.72%167.5</t>
+          <t>-7.34%959</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.72%</t>
+          <t>-7.34%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>167.5</v>
+        <v>959</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.16%211,000</t>
+          <t>0.22%50,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>211000</v>
+        <v>50000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.73%236.5</t>
+          <t>-6.57%156.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.73%</t>
+          <t>-6.57%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>236.5</v>
+        <v>156.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.11%100,000</t>
+          <t>0.15%211,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>100000</v>
+        <v>211000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+3.16%277.5</t>
+          <t>-3.81%227.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+3.16%</t>
+          <t>-3.81%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>277.5</v>
+        <v>227.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.05%42,650</t>
+          <t>0.11%100,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>42650</v>
+        <v>100000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.23%237.5</t>
+          <t>-2.88%269.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>237.5</v>
+        <v>269.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.04%34,000</t>
+          <t>0.05%42,650</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>34000</v>
+        <v>42650</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+5.58%6335</t>
+          <t>-0.42%236.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+5.58%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6335</v>
+        <v>236.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.03%1,000</t>
+          <t>0.04%34,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>34000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:19</t>
+          <t>2026-10-29 23:21:35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.5%439.5</t>
+          <t>-8.21%5815</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>-8.21%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>439.5</v>
+        <v>5815</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.02%10,217</t>
+          <t>0.03%1,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>10217</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+8.73%3800</t>
+          <t>-2.5%428.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+8.73%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3800</v>
+        <v>428.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.02%1,000</t>
+          <t>0.02%10,217</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>10217</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+4.49%128</t>
+          <t>-3.16%3680</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+4.49%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>128</v>
+        <v>3680</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.02%28,000</t>
+          <t>0.02%1,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>28000</v>
+        <v>1000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.29%689</t>
+          <t>-2.32%673</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-2.32%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+9.97%3200</t>
+          <t>-9.77%115.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3200</v>
+        <v>115.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.01%28,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>28000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+2.51%285.5</t>
+          <t>-10%2880</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+2.51%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>285.5</v>
+        <v>2880</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.01%10,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.84%1200</t>
+          <t>-3.68%275</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1200</v>
+        <v>275</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.01%2,000</t>
+          <t>0.01%10,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+2.91%441.5</t>
+          <t>+3.33%1240</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+2.91%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>441.5</v>
+        <v>1240</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>&lt;0.01%5,000</t>
+          <t>0.01%2,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+6.76%695</t>
+          <t>-1.93%433</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+6.76%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>695</v>
+        <v>433</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>&lt;0.01%3,000</t>
+          <t>0.01%5,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.56%1955</t>
+          <t>-1.73%683</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.56%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1955</v>
+        <v>683</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%3,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3605宏致</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+9.94%171.5</t>
+          <t>-2.81%1900</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>171.5</v>
+        <v>1900</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>&lt;0.01%10,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3605宏致</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+7.23%319</t>
+          <t>-3.5%165.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+7.23%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>319</v>
+        <v>165.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;0.01%5,000</t>
+          <t>&lt;0.01%10,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+5.1%1340</t>
+          <t>-2.19%312</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1340</v>
+        <v>312</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%5,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,21 +3066,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%1140</t>
+          <t>-3.73%1290</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.73%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1140</v>
+        <v>1290</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+3.61%100.5</t>
+          <t>+0.88%1150</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>100.5</v>
+        <v>1150</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>&lt;0.01%10,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:20</t>
+          <t>2026-10-29 23:21:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+8.22%803</t>
+          <t>-3.28%97.2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+8.22%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>803</v>
+        <v>97.2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%10,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">

--- a/etf_holdings/2026-10-29_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
